--- a/artfynd/A 3046-2022 artfynd.xlsx
+++ b/artfynd/A 3046-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130334353</v>
       </c>
       <c r="B2" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 3046-2022 artfynd.xlsx
+++ b/artfynd/A 3046-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130334353</v>
       </c>
       <c r="B2" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 3046-2022 artfynd.xlsx
+++ b/artfynd/A 3046-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130334353</v>
       </c>
       <c r="B2" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 3046-2022 artfynd.xlsx
+++ b/artfynd/A 3046-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130334353</v>
       </c>
       <c r="B2" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 3046-2022 artfynd.xlsx
+++ b/artfynd/A 3046-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130334353</v>
       </c>
       <c r="B2" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 3046-2022 artfynd.xlsx
+++ b/artfynd/A 3046-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130334353</v>
       </c>
       <c r="B2" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 3046-2022 artfynd.xlsx
+++ b/artfynd/A 3046-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,11 +678,11 @@
         <v>130334353</v>
       </c>
       <c r="B2" t="n">
-        <v>79221</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -769,6 +769,218 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>4144510</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>SKARVBERGET (23H1c01), Ly lm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>598733</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7208003</v>
+      </c>
+      <c r="S3" t="n">
+        <v>100</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>1996-07-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1996-07-01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>230712011 / LYCO COM / Tämligen allmän (2)  / OBJ.AREA:2,4 ha</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Carl-axel Christofersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6684977</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>SKARVBERGET (23H1c01), Ly lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>598733</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7208003</v>
+      </c>
+      <c r="S4" t="n">
+        <v>100</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1996-07-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1996-07-01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>230712011 / BRY FREM / Allmän-riklig (3)  / OBJ.AREA:2,4 ha</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Carl-axel Christofersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
